--- a/RFLTools Command Reference.xlsx
+++ b/RFLTools Command Reference.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\LISP\GitHub\RFLTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A11F6-A578-422B-8DBA-300F6AC9BCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C07E912-3EC5-4EE7-9707-AC799F7FF1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19755" yWindow="1140" windowWidth="22050" windowHeight="23370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="707">
   <si>
     <t>RFL Tools Command Listing</t>
   </si>
@@ -2140,6 +2140,12 @@
   </si>
   <si>
     <t>RFL:GETATTVALUE</t>
+  </si>
+  <si>
+    <t>SPLITSURFACESLANDXML</t>
+  </si>
+  <si>
+    <t>Writes a series of LandXML files for each surface located in the user selected LandXML file.</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -3746,1945 +3752,1953 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B157" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>338</v>
+        <v>702</v>
       </c>
       <c r="B158" t="s">
-        <v>339</v>
+        <v>703</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>226</v>
+        <v>338</v>
       </c>
       <c r="B159" t="s">
-        <v>227</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="B161" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="B162" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="B163" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>232</v>
+        <v>313</v>
       </c>
       <c r="B164" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B165" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>684</v>
+        <v>236</v>
       </c>
       <c r="B167" t="s">
-        <v>685</v>
+        <v>237</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>238</v>
+        <v>684</v>
       </c>
       <c r="B168" t="s">
-        <v>239</v>
+        <v>685</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B169" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B170" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="B171" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="B172" t="s">
-        <v>371</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B173" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>244</v>
+        <v>368</v>
       </c>
       <c r="B174" t="s">
-        <v>245</v>
+        <v>369</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B175" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B177" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B178" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B179" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B180" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B181" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B182" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B183" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B184" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B185" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B186" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B187" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B188" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B189" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B190" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B191" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B192" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B193" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B194" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="B195" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="B196" t="s">
-        <v>361</v>
+        <v>306</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>360</v>
+      </c>
+      <c r="B197" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
         <v>362</v>
       </c>
-      <c r="B197" t="s">
+      <c r="B198" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A201" s="1" t="s">
+    <row r="202" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="B202" s="1" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>490</v>
+        <v>390</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>374</v>
+        <v>490</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>673</v>
+        <v>374</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>391</v>
+        <v>673</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>472</v>
+        <v>391</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>375</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>541</v>
+        <v>394</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>487</v>
+        <v>544</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>377</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>510</v>
+        <v>377</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>378</v>
+        <v>511</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>539</v>
+        <v>378</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>379</v>
+        <v>540</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>554</v>
+        <v>379</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>380</v>
+        <v>554</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>538</v>
+        <v>399</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>444</v>
+        <v>538</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>521</v>
+        <v>417</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>462</v>
+        <v>521</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>545</v>
+        <v>446</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>400</v>
+        <v>545</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>522</v>
+        <v>381</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>418</v>
+        <v>524</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>469</v>
+        <v>420</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>401</v>
+        <v>469</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>677</v>
+        <v>485</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>704</v>
+        <v>677</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>471</v>
+        <v>704</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>516</v>
+        <v>471</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>491</v>
+        <v>519</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>488</v>
+        <v>559</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>537</v>
+        <v>488</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>676</v>
+        <v>489</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>558</v>
+        <v>679</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>482</v>
+        <v>558</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>546</v>
+        <v>482</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>483</v>
+        <v>548</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>402</v>
+        <v>483</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>509</v>
+        <v>402</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>549</v>
+        <v>509</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>494</v>
+        <v>549</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>555</v>
+        <v>494</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>675</v>
+        <v>555</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>421</v>
+        <v>675</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>550</v>
+        <v>431</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>495</v>
+        <v>551</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>526</v>
+        <v>470</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>678</v>
+        <v>527</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>568</v>
+        <v>691</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>499</v>
+        <v>568</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>403</v>
+        <v>500</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>552</v>
+        <v>404</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>473</v>
+        <v>529</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>405</v>
+        <v>473</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>689</v>
-      </c>
-      <c r="B312" t="s">
-        <v>690</v>
+        <v>405</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>406</v>
+        <v>689</v>
+      </c>
+      <c r="B313" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>566</v>
+        <v>406</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>373</v>
+        <v>566</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>520</v>
+        <v>373</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>683</v>
+        <v>518</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>517</v>
+        <v>683</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>556</v>
+        <v>517</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>474</v>
+        <v>536</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>382</v>
+        <v>474</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>530</v>
+        <v>407</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>383</v>
+        <v>553</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>531</v>
+        <v>383</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>560</v>
+        <v>531</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>475</v>
+        <v>560</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>476</v>
+        <v>512</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>384</v>
+        <v>476</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>692</v>
+        <v>411</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>502</v>
+        <v>692</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>699</v>
+        <v>504</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>508</v>
+        <v>699</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>386</v>
+        <v>508</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>450</v>
+        <v>386</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>695</v>
+        <v>464</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>477</v>
+        <v>695</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>557</v>
+        <v>477</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>561</v>
+        <v>532</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>387</v>
+        <v>514</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>455</v>
+        <v>387</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>698</v>
+        <v>443</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>533</v>
+        <v>698</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>412</v>
+        <v>533</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>478</v>
+        <v>412</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>515</v>
+        <v>466</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>562</v>
+        <v>515</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>388</v>
+        <v>562</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>534</v>
+        <v>388</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>680</v>
+        <v>535</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>567</v>
+        <v>680</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>456</v>
+        <v>563</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>458</v>
+        <v>414</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>701</v>
+        <v>501</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>415</v>
+        <v>700</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="420" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A420" s="1" t="s">
+    <row r="421" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B420" s="1" t="s">
+      <c r="B421" s="1" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>582</v>
+        <v>622</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>602</v>
+        <v>572</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>621</v>
+        <v>589</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>623</v>
+        <v>575</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>633</v>
+        <v>596</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>597</v>
+        <v>634</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>578</v>
+        <v>619</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>626</v>
+        <v>578</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>576</v>
+        <v>627</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>618</v>
+        <v>571</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>632</v>
+        <v>577</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>579</v>
+        <v>632</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>670</v>
+        <v>579</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>389</v>
+        <v>670</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>574</v>
+        <v>389</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>629</v>
+        <v>574</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="492" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A492" s="1" t="s">
+    <row r="493" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A493" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B492" s="1"/>
-    </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
-        <v>637</v>
-      </c>
+      <c r="B493" s="1"/>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="504" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="505" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="506" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>688</v>
+        <v>648</v>
       </c>
     </row>
     <row r="507" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>649</v>
+        <v>688</v>
       </c>
     </row>
     <row r="508" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>147</v>
+        <v>649</v>
       </c>
     </row>
     <row r="509" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>650</v>
+        <v>147</v>
       </c>
     </row>
     <row r="510" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="511" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="512" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="513" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="514" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="515" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="516" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>190</v>
+        <v>656</v>
       </c>
     </row>
     <row r="517" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>657</v>
+        <v>190</v>
       </c>
     </row>
     <row r="518" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="519" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="520" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="521" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="522" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="523" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="524" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="525" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="526" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="527" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="528" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="529" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
         <v>669</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A494:A529">
-    <sortCondition ref="A494:A529"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A495:A530">
+    <sortCondition ref="A495:A530"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
